--- a/TestFiles/ExcelFiles/DeptPerDiemDayStay.xlsx
+++ b/TestFiles/ExcelFiles/DeptPerDiemDayStay.xlsx
@@ -101,7 +101,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>9.92</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="2">
@@ -109,7 +109,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>8.02</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="3">
@@ -117,7 +117,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4.95</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="4">
@@ -125,7 +125,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>11.08</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="5">
@@ -133,7 +133,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>11.48</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="6">
@@ -141,7 +141,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>11.92</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="7">
@@ -149,7 +149,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>9.06</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
@@ -157,7 +157,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>3.64</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="9">
@@ -165,7 +165,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>6.62</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="10">
@@ -173,7 +173,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>9.85</v>
+        <v>7.46</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/DeptPerDiemDayStay.xlsx
+++ b/TestFiles/ExcelFiles/DeptPerDiemDayStay.xlsx
@@ -101,7 +101,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>6.83</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="2">
@@ -109,7 +109,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4.81</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="3">
@@ -117,7 +117,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>12.3</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="4">
@@ -125,7 +125,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>2.77</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="5">
@@ -133,7 +133,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>12.09</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="6">
@@ -141,7 +141,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>6.42</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="7">
@@ -149,7 +149,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>9.69</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="8">
@@ -157,7 +157,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>9.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="9">
@@ -165,7 +165,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>8.92</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="10">
@@ -173,7 +173,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>10.04</v>
+        <v>5.16</v>
       </c>
     </row>
   </sheetData>
